--- a/output/processed_props.xlsx
+++ b/output/processed_props.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="58">
   <si>
     <t>Player</t>
   </si>
@@ -49,46 +49,46 @@
     <t>Diff%</t>
   </si>
   <si>
-    <t>Jimmy Butler</t>
-  </si>
-  <si>
     <t>Stephen Curry</t>
   </si>
   <si>
-    <t>Buddy Hield</t>
+    <t>Moses Moody</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
   </si>
   <si>
     <t>Deni Avdija</t>
   </si>
   <si>
-    <t>Shaedon Sharpe</t>
+    <t>Jimmy Butler</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Toumani Camara</t>
+  </si>
+  <si>
+    <t>Robert Williams</t>
+  </si>
+  <si>
+    <t>Kris Murray</t>
+  </si>
+  <si>
+    <t>Donovan Clingan</t>
   </si>
   <si>
     <t>Jerami Grant</t>
   </si>
   <si>
-    <t>Robert Williams</t>
-  </si>
-  <si>
-    <t>Moses Moody</t>
-  </si>
-  <si>
     <t>Brandin Podziemski</t>
   </si>
   <si>
-    <t>Toumani Camara</t>
-  </si>
-  <si>
-    <t>Draymond Green</t>
-  </si>
-  <si>
-    <t>Donovan Clingan</t>
-  </si>
-  <si>
-    <t>Quinten Post</t>
-  </si>
-  <si>
-    <t>Kris Murray</t>
+    <t>Buddy Hield</t>
   </si>
   <si>
     <t>GSW</t>
@@ -97,61 +97,85 @@
     <t>POR</t>
   </si>
   <si>
-    <t>RA</t>
-  </si>
-  <si>
-    <t>FG3A</t>
-  </si>
-  <si>
     <t>PRA</t>
   </si>
   <si>
     <t>FANTASY_PTS</t>
   </si>
   <si>
+    <t>PR</t>
+  </si>
+  <si>
     <t>PTS</t>
+  </si>
+  <si>
+    <t>PA</t>
   </si>
   <si>
     <t>FGA</t>
   </si>
   <si>
+    <t>FG3A</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>FG3M</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
     <t>AST</t>
+  </si>
+  <si>
+    <t>OREB</t>
+  </si>
+  <si>
+    <t>Q1_REB</t>
+  </si>
+  <si>
+    <t>1H_FG3M</t>
+  </si>
+  <si>
+    <t>1H_PTS</t>
+  </si>
+  <si>
+    <t>BLK</t>
   </si>
   <si>
     <t>REB</t>
   </si>
   <si>
-    <t>PA</t>
+    <t>Q1_PTS</t>
   </si>
   <si>
-    <t>TD</t>
-  </si>
-  <si>
-    <t>DD</t>
+    <t>FTM</t>
   </si>
   <si>
     <t>STL</t>
   </si>
   <si>
+    <t>Q1_FG3M</t>
+  </si>
+  <si>
     <t>TOV</t>
   </si>
   <si>
-    <t>BLK</t>
-  </si>
-  <si>
-    <t>FG3M</t>
-  </si>
-  <si>
-    <t>PR</t>
+    <t>1H_REB</t>
   </si>
   <si>
     <t>2025-12-14</t>
   </si>
   <si>
-    <t>Under</t>
+    <t>Over</t>
   </si>
   <si>
-    <t>Over</t>
+    <t>Under</t>
   </si>
   <si>
     <t>S Tier</t>
@@ -534,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -598,30 +622,30 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>11.5</v>
+        <v>36.5</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G2">
-        <v>9.83</v>
+        <v>39.1</v>
       </c>
       <c r="H2" s="1">
-        <v>0.7080000042915344</v>
+        <v>0.8939999938011169</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K2">
-        <v>-14.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -633,30 +657,30 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>11.5</v>
+        <v>42.25</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G3">
-        <v>9.699999999999999</v>
+        <v>43.86</v>
       </c>
       <c r="H3" s="1">
-        <v>0.671999990940094</v>
+        <v>0.8640000224113464</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K3">
-        <v>-15.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
@@ -668,65 +692,65 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>12.5</v>
+        <v>32.5</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G4">
-        <v>14.93</v>
+        <v>34.72</v>
       </c>
       <c r="H4" s="1">
-        <v>0.6420000195503235</v>
+        <v>0.8259999752044678</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K4">
-        <v>19.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>44.05</v>
+        <v>7.5</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G5">
-        <v>39.68</v>
+        <v>5.86</v>
       </c>
       <c r="H5" s="1">
-        <v>0.6190000176429749</v>
+        <v>0.8109999895095825</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K5">
-        <v>-9.9</v>
+        <v>-21.9</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -735,33 +759,33 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>28.5</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>25.68</v>
+        <v>30.11</v>
       </c>
       <c r="H6" s="1">
-        <v>0.6169999837875366</v>
+        <v>0.7260000109672546</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K6">
-        <v>-9.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -770,68 +794,68 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>17.5</v>
+        <v>25.5</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>14.98</v>
+        <v>22.77</v>
       </c>
       <c r="H7" s="1">
-        <v>0.6060000061988831</v>
+        <v>0.7099999785423279</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K7">
-        <v>-14.4</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>18.25</v>
+        <v>18.46</v>
       </c>
       <c r="H8" s="1">
-        <v>0.5960000157356262</v>
+        <v>0.6919999718666077</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K8">
-        <v>-11</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -840,173 +864,173 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G9">
-        <v>5.71</v>
+        <v>15.24</v>
       </c>
       <c r="H9" s="1">
-        <v>0.5910000205039978</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="I9" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K9">
-        <v>-23.9</v>
+        <v>-12.9</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>5.42</v>
+        <v>12.81</v>
       </c>
       <c r="H10" s="1">
-        <v>0.6850000023841858</v>
+        <v>0.7760000228881836</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K10">
-        <v>-16.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E11">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G11">
-        <v>13.18</v>
+        <v>11.1</v>
       </c>
       <c r="H11" s="1">
-        <v>0.6169999837875366</v>
+        <v>0.7110000252723694</v>
       </c>
       <c r="I11" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K11">
-        <v>-9.1</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>29.5</v>
+        <v>19.5</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G12">
-        <v>26.67</v>
+        <v>20.74</v>
       </c>
       <c r="H12" s="1">
-        <v>0.5820000171661377</v>
+        <v>0.6639999747276306</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K12">
-        <v>-9.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>7.5</v>
+        <v>31.5</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G13">
-        <v>10.66</v>
+        <v>30.34</v>
       </c>
       <c r="H13" s="1">
-        <v>0.5740000009536743</v>
+        <v>0.5970000028610229</v>
       </c>
       <c r="I13" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K13">
-        <v>42.1</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
@@ -1015,33 +1039,33 @@
         <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14">
-        <v>12.5</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G14">
-        <v>15.16</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0.5730000138282776</v>
+        <v>0.9990000128746033</v>
       </c>
       <c r="I14" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K14">
-        <v>21.3</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
@@ -1050,68 +1074,68 @@
         <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E15">
-        <v>15.5</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G15">
-        <v>17.36</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0.5709999799728394</v>
+        <v>0.9990000128746033</v>
       </c>
       <c r="I15" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K15">
-        <v>12</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16">
-        <v>31.5</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G16">
-        <v>26.07</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0.5630000233650208</v>
+        <v>0.9990000128746033</v>
       </c>
       <c r="I16" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K16">
-        <v>-17.2</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
@@ -1120,33 +1144,33 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E17">
-        <v>19.5</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G17">
-        <v>17.76</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0.5600000023841858</v>
+        <v>0.9990000128746033</v>
       </c>
       <c r="I17" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K17">
-        <v>-8.9</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
@@ -1155,25 +1179,25 @@
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>0.5</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0.9980000257492065</v>
+        <v>0.9990000128746033</v>
       </c>
       <c r="I18" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K18">
         <v>-100</v>
@@ -1181,7 +1205,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
@@ -1190,25 +1214,25 @@
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0.9440000057220459</v>
+        <v>0.9950000047683716</v>
       </c>
       <c r="I19" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K19">
         <v>-100</v>
@@ -1216,37 +1240,37 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1">
-        <v>0.8889999985694885</v>
+        <v>0.9929999709129333</v>
       </c>
       <c r="I20" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J20" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K20">
-        <v>-100</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1260,33 +1284,33 @@
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E21">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G21">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0.7390000224113464</v>
+        <v>0.9599999785423279</v>
       </c>
       <c r="I21" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J21" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K21">
-        <v>-31.3</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
@@ -1295,98 +1319,98 @@
         <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G22">
-        <v>5.5</v>
+        <v>0.15</v>
       </c>
       <c r="H22" s="1">
-        <v>0.7229999899864197</v>
+        <v>0.8880000114440918</v>
       </c>
       <c r="I22" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J22" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K22">
-        <v>-15.4</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G23">
-        <v>4.84</v>
+        <v>0.47</v>
       </c>
       <c r="H23" s="1">
-        <v>0.7220000028610229</v>
+        <v>0.8349999785423279</v>
       </c>
       <c r="I23" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J23" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K23">
-        <v>-12</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24">
         <v>1.5</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>1.49</v>
       </c>
       <c r="H24" s="1">
-        <v>0.7099999785423279</v>
+        <v>0.8209999799728394</v>
       </c>
       <c r="I24" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J24" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K24">
-        <v>-33.3</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1394,144 +1418,144 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E25">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G25">
-        <v>4.96</v>
+        <v>10.68</v>
       </c>
       <c r="H25" s="1">
-        <v>0.703000009059906</v>
+        <v>0.8180000185966492</v>
       </c>
       <c r="I25" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J25" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K25">
-        <v>-9.800000000000001</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E26">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="H26" s="1">
-        <v>0.6949999928474426</v>
+        <v>0.8159999847412109</v>
       </c>
       <c r="I26" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J26" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K26">
-        <v>-33.3</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E27">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G27">
-        <v>8.17</v>
+        <v>2.5</v>
       </c>
       <c r="H27" s="1">
-        <v>0.6940000057220459</v>
+        <v>0.8119999766349792</v>
       </c>
       <c r="I27" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J27" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K27">
-        <v>-3.9</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
         <v>39</v>
       </c>
       <c r="E28">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G28">
-        <v>2.76</v>
+        <v>0.41</v>
       </c>
       <c r="H28" s="1">
-        <v>0.6930000185966492</v>
+        <v>0.7559999823570251</v>
       </c>
       <c r="I28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J28" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K28">
-        <v>-21.1</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
@@ -1540,68 +1564,68 @@
         <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E29">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F29" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G29">
-        <v>2.93</v>
+        <v>1.28</v>
       </c>
       <c r="H29" s="1">
-        <v>0.6840000152587891</v>
+        <v>0.7269999980926514</v>
       </c>
       <c r="I29" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J29" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K29">
-        <v>17.2</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E30">
         <v>1.5</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G30">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="H30" s="1">
-        <v>0.671999990940094</v>
+        <v>0.7239999771118164</v>
       </c>
       <c r="I30" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J30" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K30">
-        <v>-32.7</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
@@ -1610,68 +1634,68 @@
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E31">
-        <v>0.5</v>
+        <v>31.75</v>
       </c>
       <c r="F31" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G31">
-        <v>0.5</v>
+        <v>31.24</v>
       </c>
       <c r="H31" s="1">
-        <v>0.6549999713897705</v>
+        <v>0.718999981880188</v>
       </c>
       <c r="I31" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J31" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K31">
-        <v>-0</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E32">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="F32" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G32">
-        <v>5.02</v>
+        <v>10.01</v>
       </c>
       <c r="H32" s="1">
-        <v>0.6480000019073486</v>
+        <v>0.7160000205039978</v>
       </c>
       <c r="I32" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J32" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K32">
-        <v>-8.699999999999999</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
@@ -1680,68 +1704,68 @@
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E33">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G33">
-        <v>0.92</v>
+        <v>4.63</v>
       </c>
       <c r="H33" s="1">
-        <v>0.640999972820282</v>
+        <v>0.6980000138282776</v>
       </c>
       <c r="I33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J33" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K33">
-        <v>-38.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E34">
-        <v>0.5</v>
+        <v>14.5</v>
       </c>
       <c r="F34" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G34">
-        <v>0.5</v>
+        <v>15.47</v>
       </c>
       <c r="H34" s="1">
-        <v>0.621999979019165</v>
+        <v>0.6930000185966492</v>
       </c>
       <c r="I34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J34" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K34">
-        <v>-0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
@@ -1750,68 +1774,68 @@
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E35">
-        <v>1.5</v>
+        <v>26.5</v>
       </c>
       <c r="F35" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G35">
-        <v>2.15</v>
+        <v>25.56</v>
       </c>
       <c r="H35" s="1">
-        <v>0.6179999709129333</v>
+        <v>0.6919999718666077</v>
       </c>
       <c r="I35" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J35" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K35">
-        <v>43.3</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E36">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F36" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G36">
-        <v>3.03</v>
+        <v>1.29</v>
       </c>
       <c r="H36" s="1">
-        <v>0.6140000224113464</v>
+        <v>0.6890000104904175</v>
       </c>
       <c r="I36" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J36" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K36">
-        <v>21.2</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
@@ -1820,98 +1844,98 @@
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E37">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G37">
-        <v>11.6</v>
+        <v>1.48</v>
       </c>
       <c r="H37" s="1">
-        <v>0.6140000224113464</v>
+        <v>0.6779999732971191</v>
       </c>
       <c r="I37" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J37" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K37">
-        <v>0.9</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E38">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G38">
-        <v>7.16</v>
+        <v>1.49</v>
       </c>
       <c r="H38" s="1">
-        <v>0.6140000224113464</v>
+        <v>0.6779999732971191</v>
       </c>
       <c r="I38" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J38" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K38">
-        <v>-4.5</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E39">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G39">
-        <v>5.73</v>
+        <v>1.29</v>
       </c>
       <c r="H39" s="1">
-        <v>0.6060000061988831</v>
+        <v>0.675000011920929</v>
       </c>
       <c r="I39" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J39" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K39">
-        <v>-11.8</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1919,39 +1943,39 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E40">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G40">
-        <v>2.03</v>
+        <v>6.49</v>
       </c>
       <c r="H40" s="1">
-        <v>0.5889999866485596</v>
+        <v>0.6710000038146973</v>
       </c>
       <c r="I40" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J40" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K40">
-        <v>35.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
         <v>25</v>
@@ -1960,103 +1984,103 @@
         <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E41">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G41">
-        <v>2.34</v>
+        <v>8.9</v>
       </c>
       <c r="H41" s="1">
-        <v>0.5839999914169312</v>
+        <v>0.6690000295639038</v>
       </c>
       <c r="I41" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J41" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K41">
-        <v>56</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E42">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G42">
-        <v>7.22</v>
+        <v>3.12</v>
       </c>
       <c r="H42" s="1">
-        <v>0.5830000042915344</v>
+        <v>0.6620000004768372</v>
       </c>
       <c r="I42" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J42" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K42">
-        <v>-3.7</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E43">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G43">
-        <v>4.07</v>
+        <v>15.49</v>
       </c>
       <c r="H43" s="1">
-        <v>0.5820000171661377</v>
+        <v>0.6579999923706055</v>
       </c>
       <c r="I43" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J43" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K43">
-        <v>-9.6</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s">
         <v>25</v>
@@ -2065,68 +2089,68 @@
         <v>26</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E44">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F44" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G44">
-        <v>3.1</v>
+        <v>1.45</v>
       </c>
       <c r="H44" s="1">
-        <v>0.5820000171661377</v>
+        <v>0.6549999713897705</v>
       </c>
       <c r="I44" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J44" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K44">
-        <v>24</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E45">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G45">
-        <v>5.24</v>
+        <v>14.74</v>
       </c>
       <c r="H45" s="1">
-        <v>0.5799999833106995</v>
+        <v>0.6510000228881836</v>
       </c>
       <c r="I45" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J45" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K45">
-        <v>-4.7</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
         <v>25</v>
@@ -2135,33 +2159,33 @@
         <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E46">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G46">
-        <v>0.98</v>
+        <v>5.79</v>
       </c>
       <c r="H46" s="1">
-        <v>0.5699999928474426</v>
+        <v>0.6399999856948853</v>
       </c>
       <c r="I46" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J46" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K46">
-        <v>-34.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
         <v>25</v>
@@ -2170,33 +2194,33 @@
         <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E47">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F47" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G47">
-        <v>4.26</v>
+        <v>1.33</v>
       </c>
       <c r="H47" s="1">
-        <v>0.5649999976158142</v>
+        <v>0.6380000114440918</v>
       </c>
       <c r="I47" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J47" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K47">
-        <v>-5.3</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
         <v>25</v>
@@ -2205,33 +2229,33 @@
         <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E48">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G48">
-        <v>9.949999999999999</v>
+        <v>4.93</v>
       </c>
       <c r="H48" s="1">
-        <v>0.5649999976158142</v>
+        <v>0.6240000128746033</v>
       </c>
       <c r="I48" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J48" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K48">
-        <v>17.1</v>
+        <v>-10.4</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
         <v>25</v>
@@ -2240,68 +2264,68 @@
         <v>26</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E49">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G49">
-        <v>2.51</v>
+        <v>1.6</v>
       </c>
       <c r="H49" s="1">
-        <v>0.5619999766349792</v>
+        <v>0.621999979019165</v>
       </c>
       <c r="I49" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J49" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K49">
-        <v>0.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E50">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F50" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G50">
-        <v>1.48</v>
+        <v>7.26</v>
       </c>
       <c r="H50" s="1">
-        <v>0.5619999766349792</v>
+        <v>0.6190000176429749</v>
       </c>
       <c r="I50" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J50" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K50">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
         <v>25</v>
@@ -2310,68 +2334,68 @@
         <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E51">
-        <v>4.5</v>
+        <v>32.5</v>
       </c>
       <c r="F51" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G51">
-        <v>4.93</v>
+        <v>33.28</v>
       </c>
       <c r="H51" s="1">
-        <v>0.5590000152587891</v>
+        <v>0.6179999709129333</v>
       </c>
       <c r="I51" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J51" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K51">
-        <v>9.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E52">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="F52" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G52">
-        <v>13.6</v>
+        <v>4.4</v>
       </c>
       <c r="H52" s="1">
-        <v>0.5580000281333923</v>
+        <v>0.6150000095367432</v>
       </c>
       <c r="I52" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J52" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K52">
-        <v>-6.2</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
@@ -2380,68 +2404,68 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E53">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F53" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G53">
-        <v>1.09</v>
+        <v>6.61</v>
       </c>
       <c r="H53" s="1">
-        <v>0.5580000281333923</v>
+        <v>0.6140000224113464</v>
       </c>
       <c r="I53" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J53" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K53">
-        <v>-27.3</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E54">
-        <v>38.5</v>
+        <v>31.5</v>
       </c>
       <c r="F54" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G54">
-        <v>35.22</v>
+        <v>31.46</v>
       </c>
       <c r="H54" s="1">
-        <v>0.5509999990463257</v>
+        <v>0.6129999756813049</v>
       </c>
       <c r="I54" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J54" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K54">
-        <v>-8.5</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
         <v>25</v>
@@ -2450,63 +2474,63 @@
         <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E55">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F55" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G55">
-        <v>10.85</v>
+        <v>4.56</v>
       </c>
       <c r="H55" s="1">
-        <v>0.550000011920929</v>
+        <v>0.6069999933242798</v>
       </c>
       <c r="I55" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J55" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K55">
-        <v>44.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E56">
-        <v>21.5</v>
+        <v>1.5</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G56">
-        <v>19.32</v>
+        <v>1.58</v>
       </c>
       <c r="H56" s="1">
-        <v>0.546999990940094</v>
+        <v>0.6069999933242798</v>
       </c>
       <c r="I56" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J56" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K56">
-        <v>-10.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2514,39 +2538,39 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E57">
-        <v>15.5</v>
+        <v>8.5</v>
       </c>
       <c r="F57" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G57">
-        <v>13.99</v>
+        <v>9.27</v>
       </c>
       <c r="H57" s="1">
-        <v>0.546999990940094</v>
+        <v>0.5979999899864197</v>
       </c>
       <c r="I57" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J57" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K57">
-        <v>-9.699999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
         <v>26</v>
@@ -2555,33 +2579,33 @@
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E58">
-        <v>22.5</v>
+        <v>3.5</v>
       </c>
       <c r="F58" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G58">
-        <v>19.95</v>
+        <v>3.33</v>
       </c>
       <c r="H58" s="1">
-        <v>0.5370000004768372</v>
+        <v>0.5950000286102295</v>
       </c>
       <c r="I58" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J58" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K58">
-        <v>-11.3</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B59" t="s">
         <v>25</v>
@@ -2590,68 +2614,68 @@
         <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E59">
-        <v>24.5</v>
+        <v>2.5</v>
       </c>
       <c r="F59" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G59">
-        <v>21.16</v>
+        <v>2.49</v>
       </c>
       <c r="H59" s="1">
-        <v>0.531000018119812</v>
+        <v>0.5910000205039978</v>
       </c>
       <c r="I59" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J59" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K59">
-        <v>-13.6</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D60" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E60">
-        <v>23.5</v>
+        <v>1.5</v>
       </c>
       <c r="F60" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G60">
-        <v>21.42</v>
+        <v>1.57</v>
       </c>
       <c r="H60" s="1">
-        <v>0.5249999761581421</v>
+        <v>0.5899999737739563</v>
       </c>
       <c r="I60" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J60" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K60">
-        <v>-8.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B61" t="s">
         <v>26</v>
@@ -2660,33 +2684,33 @@
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E61">
         <v>9.5</v>
       </c>
       <c r="F61" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G61">
-        <v>12.22</v>
+        <v>9.27</v>
       </c>
       <c r="H61" s="1">
-        <v>0.5210000276565552</v>
+        <v>0.5849999785423279</v>
       </c>
       <c r="I61" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J61" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K61">
-        <v>28.6</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
         <v>25</v>
@@ -2695,168 +2719,168 @@
         <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E62">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F62" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G62">
-        <v>9.52</v>
+        <v>4.52</v>
       </c>
       <c r="H62" s="1">
-        <v>0.5199999809265137</v>
+        <v>0.5849999785423279</v>
       </c>
       <c r="I62" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J62" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K62">
-        <v>26.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E63">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="F63" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G63">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="H63" s="1">
-        <v>0.5109999775886536</v>
+        <v>0.5809999704360962</v>
       </c>
       <c r="I63" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J63" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K63">
-        <v>-13.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E64">
-        <v>0.5</v>
+        <v>26.5</v>
       </c>
       <c r="F64" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H64" s="1">
-        <v>0.9869999885559082</v>
+        <v>0.5759999752044678</v>
       </c>
       <c r="I64" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J64" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K64">
-        <v>-100</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E65">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F65" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="H65" s="1">
-        <v>0.9850000143051147</v>
+        <v>0.574999988079071</v>
       </c>
       <c r="I65" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J65" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K65">
-        <v>-100</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E66">
-        <v>0.5</v>
+        <v>14.5</v>
       </c>
       <c r="F66" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>15.15</v>
       </c>
       <c r="H66" s="1">
-        <v>0.9810000061988831</v>
+        <v>0.5699999928474426</v>
       </c>
       <c r="I66" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J66" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K66">
-        <v>-100</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -2864,139 +2888,139 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D67" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E67">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="F67" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="H67" s="1">
-        <v>0.9739999771118164</v>
+        <v>0.5609999895095825</v>
       </c>
       <c r="I67" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J67" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K67">
-        <v>-100</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E68">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F68" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G68">
-        <v>6.47</v>
+        <v>5.57</v>
       </c>
       <c r="H68" s="1">
-        <v>0.7039999961853027</v>
+        <v>0.5600000023841858</v>
       </c>
       <c r="I68" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J68" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K68">
-        <v>-0.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D69" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E69">
-        <v>10.5</v>
+        <v>24.5</v>
       </c>
       <c r="F69" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G69">
-        <v>9.84</v>
+        <v>25.11</v>
       </c>
       <c r="H69" s="1">
-        <v>0.6159999966621399</v>
+        <v>0.5569999814033508</v>
       </c>
       <c r="I69" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J69" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K69">
-        <v>-6.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E70">
-        <v>4.5</v>
+        <v>29.5</v>
       </c>
       <c r="F70" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G70">
-        <v>3.49</v>
+        <v>26.6</v>
       </c>
       <c r="H70" s="1">
-        <v>0.6140000224113464</v>
+        <v>0.5339999794960022</v>
       </c>
       <c r="I70" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J70" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K70">
-        <v>-22.4</v>
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3004,109 +3028,109 @@
         <v>24</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E71">
-        <v>0.5</v>
+        <v>12.5</v>
       </c>
       <c r="F71" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G71">
-        <v>0.67</v>
+        <v>14.05</v>
       </c>
       <c r="H71" s="1">
-        <v>0.6079999804496765</v>
+        <v>0.531000018119812</v>
       </c>
       <c r="I71" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J71" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K71">
-        <v>34</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E72">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G72">
-        <v>4.55</v>
+        <v>0.53</v>
       </c>
       <c r="H72" s="1">
-        <v>0.6000000238418579</v>
+        <v>0.9049999713897705</v>
       </c>
       <c r="I72" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J72" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K72">
-        <v>1.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E73">
         <v>1.5</v>
       </c>
       <c r="F73" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G73">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="H73" s="1">
-        <v>0.5879999995231628</v>
+        <v>0.8560000061988831</v>
       </c>
       <c r="I73" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J73" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K73">
-        <v>-7.3</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" t="s">
         <v>25</v>
@@ -3115,33 +3139,33 @@
         <v>26</v>
       </c>
       <c r="D74" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E74">
-        <v>36.5</v>
+        <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G74">
-        <v>34.14</v>
+        <v>0.53</v>
       </c>
       <c r="H74" s="1">
-        <v>0.5730000138282776</v>
+        <v>0.8140000104904175</v>
       </c>
       <c r="I74" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J74" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K74">
-        <v>-6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B75" t="s">
         <v>25</v>
@@ -3150,33 +3174,33 @@
         <v>26</v>
       </c>
       <c r="D75" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E75">
-        <v>31.5</v>
+        <v>7.5</v>
       </c>
       <c r="F75" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G75">
-        <v>29.67</v>
+        <v>7.63</v>
       </c>
       <c r="H75" s="1">
-        <v>0.5690000057220459</v>
+        <v>0.7689999938011169</v>
       </c>
       <c r="I75" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J75" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K75">
-        <v>-5.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B76" t="s">
         <v>26</v>
@@ -3185,68 +3209,68 @@
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E76">
-        <v>25.5</v>
+        <v>4.5</v>
       </c>
       <c r="F76" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G76">
-        <v>22.43</v>
+        <v>4.36</v>
       </c>
       <c r="H76" s="1">
-        <v>0.5659999847412109</v>
+        <v>0.7220000028610229</v>
       </c>
       <c r="I76" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J76" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K76">
-        <v>-12</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E77">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="F77" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G77">
-        <v>1.77</v>
+        <v>10.5</v>
       </c>
       <c r="H77" s="1">
-        <v>0.5640000104904175</v>
+        <v>0.7089999914169312</v>
       </c>
       <c r="I77" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J77" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K77">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B78" t="s">
         <v>26</v>
@@ -3255,63 +3279,63 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E78">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F78" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G78">
-        <v>9.4</v>
+        <v>7.42</v>
       </c>
       <c r="H78" s="1">
-        <v>0.5640000104904175</v>
+        <v>0.6679999828338623</v>
       </c>
       <c r="I78" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J78" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K78">
-        <v>10.6</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E79">
         <v>1.5</v>
       </c>
       <c r="F79" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G79">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="H79" s="1">
-        <v>0.5600000023841858</v>
+        <v>0.6650000214576721</v>
       </c>
       <c r="I79" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J79" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K79">
-        <v>14.7</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3325,33 +3349,33 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E80">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="F80" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G80">
-        <v>6.82</v>
+        <v>12.35</v>
       </c>
       <c r="H80" s="1">
-        <v>0.5550000071525574</v>
+        <v>0.6489999890327454</v>
       </c>
       <c r="I80" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J80" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K80">
-        <v>-9.1</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B81" t="s">
         <v>26</v>
@@ -3360,33 +3384,33 @@
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E81">
-        <v>13.5</v>
+        <v>2.5</v>
       </c>
       <c r="F81" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G81">
-        <v>13.81</v>
+        <v>2.45</v>
       </c>
       <c r="H81" s="1">
-        <v>0.5540000200271606</v>
+        <v>0.6399999856948853</v>
       </c>
       <c r="I81" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J81" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K81">
-        <v>2.3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B82" t="s">
         <v>26</v>
@@ -3395,33 +3419,33 @@
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E82">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="F82" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G82">
-        <v>5.81</v>
+        <v>0.5</v>
       </c>
       <c r="H82" s="1">
-        <v>0.5519999861717224</v>
+        <v>0.6330000162124634</v>
       </c>
       <c r="I82" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J82" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K82">
-        <v>-10.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
         <v>25</v>
@@ -3430,33 +3454,33 @@
         <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E83">
-        <v>32.5</v>
+        <v>5.5</v>
       </c>
       <c r="F83" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G83">
-        <v>28.9</v>
+        <v>5.67</v>
       </c>
       <c r="H83" s="1">
-        <v>0.5509999990463257</v>
+        <v>0.6209999918937683</v>
       </c>
       <c r="I83" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J83" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K83">
-        <v>-11.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B84" t="s">
         <v>26</v>
@@ -3465,33 +3489,33 @@
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E84">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
       <c r="F84" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G84">
-        <v>20.18</v>
+        <v>6.43</v>
       </c>
       <c r="H84" s="1">
-        <v>0.550000011920929</v>
+        <v>0.6169999837875366</v>
       </c>
       <c r="I84" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J84" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K84">
-        <v>-1.6</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B85" t="s">
         <v>26</v>
@@ -3500,33 +3524,33 @@
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E85">
         <v>4.5</v>
       </c>
       <c r="F85" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G85">
-        <v>5.97</v>
+        <v>4.61</v>
       </c>
       <c r="H85" s="1">
-        <v>0.5490000247955322</v>
+        <v>0.6169999837875366</v>
       </c>
       <c r="I85" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J85" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K85">
-        <v>32.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
         <v>26</v>
@@ -3535,33 +3559,33 @@
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E86">
-        <v>31.25</v>
+        <v>2.5</v>
       </c>
       <c r="F86" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G86">
-        <v>30.31</v>
+        <v>2.69</v>
       </c>
       <c r="H86" s="1">
-        <v>0.546999990940094</v>
+        <v>0.6140000224113464</v>
       </c>
       <c r="I86" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J86" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K86">
-        <v>-3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B87" t="s">
         <v>26</v>
@@ -3570,33 +3594,33 @@
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E87">
-        <v>6.5</v>
+        <v>38.5</v>
       </c>
       <c r="F87" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G87">
-        <v>6.52</v>
+        <v>37.9</v>
       </c>
       <c r="H87" s="1">
-        <v>0.5460000038146973</v>
+        <v>0.6110000014305115</v>
       </c>
       <c r="I87" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J87" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K87">
-        <v>0.3</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
         <v>25</v>
@@ -3605,33 +3629,33 @@
         <v>26</v>
       </c>
       <c r="D88" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E88">
-        <v>1.5</v>
+        <v>21.5</v>
       </c>
       <c r="F88" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G88">
-        <v>1.55</v>
+        <v>21.12</v>
       </c>
       <c r="H88" s="1">
-        <v>0.5460000038146973</v>
+        <v>0.6110000014305115</v>
       </c>
       <c r="I88" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J88" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K88">
-        <v>3.3</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B89" t="s">
         <v>26</v>
@@ -3640,68 +3664,68 @@
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E89">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="F89" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G89">
-        <v>5.55</v>
+        <v>2.58</v>
       </c>
       <c r="H89" s="1">
-        <v>0.5460000038146973</v>
+        <v>0.609000027179718</v>
       </c>
       <c r="I89" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J89" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K89">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E90">
-        <v>31.75</v>
+        <v>4.5</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G90">
-        <v>30.87</v>
+        <v>4.21</v>
       </c>
       <c r="H90" s="1">
-        <v>0.5450000166893005</v>
+        <v>0.6050000190734863</v>
       </c>
       <c r="I90" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J90" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K90">
-        <v>-2.8</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B91" t="s">
         <v>25</v>
@@ -3710,28 +3734,28 @@
         <v>26</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E91">
-        <v>9.5</v>
+        <v>25.5</v>
       </c>
       <c r="F91" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G91">
-        <v>9.130000000000001</v>
+        <v>25.37</v>
       </c>
       <c r="H91" s="1">
-        <v>0.5440000295639038</v>
+        <v>0.6010000109672546</v>
       </c>
       <c r="I91" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J91" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K91">
-        <v>-3.9</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3745,68 +3769,68 @@
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E92">
-        <v>4.5</v>
+        <v>31.5</v>
       </c>
       <c r="F92" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G92">
-        <v>4.56</v>
+        <v>32.49</v>
       </c>
       <c r="H92" s="1">
-        <v>0.5440000295639038</v>
+        <v>0.5979999899864197</v>
       </c>
       <c r="I92" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J92" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K92">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E93">
-        <v>32.5</v>
+        <v>8.5</v>
       </c>
       <c r="F93" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G93">
-        <v>29.65</v>
+        <v>8.67</v>
       </c>
       <c r="H93" s="1">
-        <v>0.5419999957084656</v>
+        <v>0.5920000076293945</v>
       </c>
       <c r="I93" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J93" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K93">
-        <v>-8.800000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B94" t="s">
         <v>26</v>
@@ -3815,138 +3839,138 @@
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E94">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="F94" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G94">
-        <v>2.46</v>
+        <v>5.05</v>
       </c>
       <c r="H94" s="1">
-        <v>0.5419999957084656</v>
+        <v>0.5920000076293945</v>
       </c>
       <c r="I94" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J94" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K94">
-        <v>-1.6</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E95">
-        <v>39.05</v>
+        <v>44.05</v>
       </c>
       <c r="F95" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G95">
-        <v>36.81</v>
+        <v>44.55</v>
       </c>
       <c r="H95" s="1">
-        <v>0.5410000085830688</v>
+        <v>0.5910000205039978</v>
       </c>
       <c r="I95" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J95" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K95">
-        <v>-5.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D96" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E96">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F96" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G96">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="H96" s="1">
-        <v>0.5320000052452087</v>
+        <v>0.5860000252723694</v>
       </c>
       <c r="I96" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J96" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K96">
-        <v>-2</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D97" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E97">
-        <v>26.5</v>
+        <v>1.5</v>
       </c>
       <c r="F97" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G97">
-        <v>25.4</v>
+        <v>1.52</v>
       </c>
       <c r="H97" s="1">
-        <v>0.531000018119812</v>
+        <v>0.5839999914169312</v>
       </c>
       <c r="I97" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J97" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K97">
-        <v>-4.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B98" t="s">
         <v>26</v>
@@ -3955,33 +3979,33 @@
         <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E98">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="F98" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G98">
-        <v>0.76</v>
+        <v>3.32</v>
       </c>
       <c r="H98" s="1">
-        <v>0.5279999971389771</v>
+        <v>0.5830000042915344</v>
       </c>
       <c r="I98" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J98" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K98">
-        <v>52</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B99" t="s">
         <v>25</v>
@@ -3990,28 +4014,28 @@
         <v>26</v>
       </c>
       <c r="D99" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E99">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F99" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G99">
-        <v>4.72</v>
+        <v>1.67</v>
       </c>
       <c r="H99" s="1">
-        <v>0.5270000100135803</v>
+        <v>0.5830000042915344</v>
       </c>
       <c r="I99" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J99" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K99">
-        <v>4.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -4025,33 +4049,33 @@
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E100">
-        <v>26.5</v>
+        <v>4.5</v>
       </c>
       <c r="F100" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G100">
-        <v>24.17</v>
+        <v>4.93</v>
       </c>
       <c r="H100" s="1">
-        <v>0.5270000100135803</v>
+        <v>0.5820000171661377</v>
       </c>
       <c r="I100" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J100" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K100">
-        <v>-8.800000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B101" t="s">
         <v>26</v>
@@ -4060,33 +4084,33 @@
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E101">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F101" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G101">
-        <v>3.45</v>
+        <v>6.29</v>
       </c>
       <c r="H101" s="1">
-        <v>0.5260000228881836</v>
+        <v>0.5789999961853027</v>
       </c>
       <c r="I101" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J101" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K101">
-        <v>-1.4</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B102" t="s">
         <v>25</v>
@@ -4095,33 +4119,33 @@
         <v>26</v>
       </c>
       <c r="D102" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E102">
         <v>2.5</v>
       </c>
       <c r="F102" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G102">
-        <v>2.33</v>
+        <v>3.26</v>
       </c>
       <c r="H102" s="1">
-        <v>0.5239999890327454</v>
+        <v>0.578000009059906</v>
       </c>
       <c r="I102" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J102" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K102">
-        <v>-6.8</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
@@ -4130,103 +4154,103 @@
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E103">
         <v>1.5</v>
       </c>
       <c r="F103" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G103">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="H103" s="1">
-        <v>0.5239999890327454</v>
+        <v>0.5720000267028809</v>
       </c>
       <c r="I103" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J103" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K103">
-        <v>34.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E104">
-        <v>42.25</v>
+        <v>7.5</v>
       </c>
       <c r="F104" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G104">
-        <v>38.73</v>
+        <v>7.36</v>
       </c>
       <c r="H104" s="1">
-        <v>0.5230000019073486</v>
+        <v>0.5720000267028809</v>
       </c>
       <c r="I104" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J104" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K104">
-        <v>-8.300000000000001</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E105">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="F105" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G105">
-        <v>3.47</v>
+        <v>12.34</v>
       </c>
       <c r="H105" s="1">
-        <v>0.5230000019073486</v>
+        <v>0.5720000267028809</v>
       </c>
       <c r="I105" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J105" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K105">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B106" t="s">
         <v>26</v>
@@ -4235,33 +4259,33 @@
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E106">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="F106" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G106">
-        <v>7.47</v>
+        <v>15.02</v>
       </c>
       <c r="H106" s="1">
-        <v>0.5210000276565552</v>
+        <v>0.5590000152587891</v>
       </c>
       <c r="I106" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J106" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K106">
-        <v>-12.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B107" t="s">
         <v>25</v>
@@ -4270,68 +4294,68 @@
         <v>26</v>
       </c>
       <c r="D107" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E107">
-        <v>25.5</v>
+        <v>7.5</v>
       </c>
       <c r="F107" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G107">
-        <v>24.16</v>
+        <v>8.74</v>
       </c>
       <c r="H107" s="1">
-        <v>0.5210000276565552</v>
+        <v>0.5580000281333923</v>
       </c>
       <c r="I107" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J107" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K107">
-        <v>-5.3</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D108" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E108">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="F108" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G108">
-        <v>21.18</v>
+        <v>2.49</v>
       </c>
       <c r="H108" s="1">
-        <v>0.5199999809265137</v>
+        <v>0.5569999814033508</v>
       </c>
       <c r="I108" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J108" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K108">
-        <v>3.3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B109" t="s">
         <v>26</v>
@@ -4340,33 +4364,33 @@
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E109">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F109" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G109">
-        <v>1.65</v>
+        <v>5.42</v>
       </c>
       <c r="H109" s="1">
-        <v>0.5180000066757202</v>
+        <v>0.5550000071525574</v>
       </c>
       <c r="I109" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J109" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K109">
-        <v>10</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B110" t="s">
         <v>26</v>
@@ -4375,68 +4399,68 @@
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E110">
         <v>2.5</v>
       </c>
       <c r="F110" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G110">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="H110" s="1">
-        <v>0.515999972820282</v>
+        <v>0.5540000200271606</v>
       </c>
       <c r="I110" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J110" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K110">
-        <v>-8.4</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E111">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F111" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G111">
-        <v>5.07</v>
+        <v>6.22</v>
       </c>
       <c r="H111" s="1">
-        <v>0.515999972820282</v>
+        <v>0.5529999732971191</v>
       </c>
       <c r="I111" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J111" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K111">
-        <v>-7.8</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B112" t="s">
         <v>25</v>
@@ -4445,33 +4469,33 @@
         <v>26</v>
       </c>
       <c r="D112" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E112">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F112" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G112">
-        <v>0.86</v>
+        <v>1.55</v>
       </c>
       <c r="H112" s="1">
-        <v>0.5149999856948853</v>
+        <v>0.5529999732971191</v>
       </c>
       <c r="I112" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J112" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K112">
-        <v>72</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B113" t="s">
         <v>26</v>
@@ -4480,68 +4504,68 @@
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E113">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F113" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G113">
-        <v>3.78</v>
+        <v>6.1</v>
       </c>
       <c r="H113" s="1">
-        <v>0.5149999856948853</v>
+        <v>0.5509999990463257</v>
       </c>
       <c r="I113" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J113" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K113">
-        <v>8</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D114" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E114">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F114" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G114">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="H114" s="1">
-        <v>0.5149999856948853</v>
+        <v>0.5509999990463257</v>
       </c>
       <c r="I114" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J114" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K114">
-        <v>4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B115" t="s">
         <v>26</v>
@@ -4550,173 +4574,173 @@
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E115">
-        <v>12.5</v>
+        <v>31.25</v>
       </c>
       <c r="F115" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G115">
-        <v>11.8</v>
+        <v>30.31</v>
       </c>
       <c r="H115" s="1">
-        <v>0.5139999985694885</v>
+        <v>0.5490000247955322</v>
       </c>
       <c r="I115" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J115" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K115">
-        <v>-5.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D116" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E116">
-        <v>31.5</v>
+        <v>2.5</v>
       </c>
       <c r="F116" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G116">
-        <v>28.74</v>
+        <v>2.52</v>
       </c>
       <c r="H116" s="1">
-        <v>0.5070000290870667</v>
+        <v>0.5479999780654907</v>
       </c>
       <c r="I116" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J116" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K116">
-        <v>-8.800000000000001</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B117" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E117">
-        <v>19.5</v>
+        <v>0.5</v>
       </c>
       <c r="F117" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G117">
-        <v>19.06</v>
+        <v>0.75</v>
       </c>
       <c r="H117" s="1">
-        <v>0.5059999823570251</v>
+        <v>0.5460000038146973</v>
       </c>
       <c r="I117" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J117" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K117">
-        <v>-2.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E118">
-        <v>16.5</v>
+        <v>2.5</v>
       </c>
       <c r="F118" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G118">
-        <v>16.03</v>
+        <v>2.6</v>
       </c>
       <c r="H118" s="1">
-        <v>0.5059999823570251</v>
+        <v>0.5450000166893005</v>
       </c>
       <c r="I118" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J118" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K118">
-        <v>-2.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D119" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E119">
         <v>2.5</v>
       </c>
       <c r="F119" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G119">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="H119" s="1">
-        <v>0.5049999952316284</v>
+        <v>0.5450000166893005</v>
       </c>
       <c r="I119" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J119" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K119">
-        <v>1.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B120" t="s">
         <v>26</v>
@@ -4725,63 +4749,63 @@
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E120">
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
       <c r="F120" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G120">
-        <v>6.43</v>
+        <v>15.69</v>
       </c>
       <c r="H120" s="1">
-        <v>0.5049999952316284</v>
+        <v>0.5440000295639038</v>
       </c>
       <c r="I120" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J120" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K120">
-        <v>-1.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B121" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E121">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F121" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G121">
-        <v>1.24</v>
+        <v>4.75</v>
       </c>
       <c r="H121" s="1">
-        <v>0.5009999871253967</v>
+        <v>0.5419999957084656</v>
       </c>
       <c r="I121" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="J121" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K121">
-        <v>-17.3</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -4789,38 +4813,1228 @@
         <v>16</v>
       </c>
       <c r="B122" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D122" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E122">
+        <v>1.5</v>
+      </c>
+      <c r="F122" t="s">
+        <v>51</v>
+      </c>
+      <c r="G122">
+        <v>1.41</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0.5419999957084656</v>
+      </c>
+      <c r="I122" t="s">
+        <v>52</v>
+      </c>
+      <c r="J122" t="s">
+        <v>57</v>
+      </c>
+      <c r="K122">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" t="s">
+        <v>22</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" t="s">
+        <v>25</v>
+      </c>
+      <c r="D123" t="s">
+        <v>30</v>
+      </c>
+      <c r="E123">
+        <v>20.5</v>
+      </c>
+      <c r="F123" t="s">
+        <v>51</v>
+      </c>
+      <c r="G123">
+        <v>21.04</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0.5410000085830688</v>
+      </c>
+      <c r="I123" t="s">
+        <v>52</v>
+      </c>
+      <c r="J123" t="s">
+        <v>57</v>
+      </c>
+      <c r="K123">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" t="s">
+        <v>16</v>
+      </c>
+      <c r="B124" t="s">
+        <v>25</v>
+      </c>
+      <c r="C124" t="s">
+        <v>26</v>
+      </c>
+      <c r="D124" t="s">
+        <v>38</v>
+      </c>
+      <c r="E124">
+        <v>5.5</v>
+      </c>
+      <c r="F124" t="s">
+        <v>51</v>
+      </c>
+      <c r="G124">
+        <v>5.86</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0.5339999794960022</v>
+      </c>
+      <c r="I124" t="s">
+        <v>53</v>
+      </c>
+      <c r="J124" t="s">
+        <v>57</v>
+      </c>
+      <c r="K124">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" t="s">
+        <v>16</v>
+      </c>
+      <c r="B125" t="s">
+        <v>25</v>
+      </c>
+      <c r="C125" t="s">
+        <v>26</v>
+      </c>
+      <c r="D125" t="s">
+        <v>45</v>
+      </c>
+      <c r="E125">
+        <v>4.5</v>
+      </c>
+      <c r="F125" t="s">
+        <v>51</v>
+      </c>
+      <c r="G125">
+        <v>4.43</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0.5329999923706055</v>
+      </c>
+      <c r="I125" t="s">
+        <v>52</v>
+      </c>
+      <c r="J125" t="s">
+        <v>57</v>
+      </c>
+      <c r="K125">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" t="s">
+        <v>16</v>
+      </c>
+      <c r="B126" t="s">
+        <v>25</v>
+      </c>
+      <c r="C126" t="s">
+        <v>26</v>
+      </c>
+      <c r="D126" t="s">
+        <v>39</v>
+      </c>
+      <c r="E126">
         <v>2.5</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F126" t="s">
+        <v>51</v>
+      </c>
+      <c r="G126">
+        <v>2.39</v>
+      </c>
+      <c r="H126" s="1">
+        <v>0.5320000052452087</v>
+      </c>
+      <c r="I126" t="s">
+        <v>53</v>
+      </c>
+      <c r="J126" t="s">
+        <v>57</v>
+      </c>
+      <c r="K126">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127" t="s">
+        <v>25</v>
+      </c>
+      <c r="C127" t="s">
+        <v>26</v>
+      </c>
+      <c r="D127" t="s">
+        <v>38</v>
+      </c>
+      <c r="E127">
+        <v>4.5</v>
+      </c>
+      <c r="F127" t="s">
+        <v>51</v>
+      </c>
+      <c r="G127">
+        <v>4.47</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0.5320000052452087</v>
+      </c>
+      <c r="I127" t="s">
+        <v>53</v>
+      </c>
+      <c r="J127" t="s">
+        <v>57</v>
+      </c>
+      <c r="K127">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" t="s">
+        <v>25</v>
+      </c>
+      <c r="D128" t="s">
+        <v>44</v>
+      </c>
+      <c r="E128">
+        <v>8.5</v>
+      </c>
+      <c r="F128" t="s">
+        <v>51</v>
+      </c>
+      <c r="G128">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0.5289999842643738</v>
+      </c>
+      <c r="I128" t="s">
+        <v>53</v>
+      </c>
+      <c r="J128" t="s">
+        <v>57</v>
+      </c>
+      <c r="K128">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" t="s">
+        <v>13</v>
+      </c>
+      <c r="B129" t="s">
+        <v>26</v>
+      </c>
+      <c r="C129" t="s">
+        <v>25</v>
+      </c>
+      <c r="D129" t="s">
+        <v>46</v>
+      </c>
+      <c r="E129">
+        <v>3.5</v>
+      </c>
+      <c r="F129" t="s">
+        <v>51</v>
+      </c>
+      <c r="G129">
+        <v>3.41</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0.5289999842643738</v>
+      </c>
+      <c r="I129" t="s">
+        <v>53</v>
+      </c>
+      <c r="J129" t="s">
+        <v>57</v>
+      </c>
+      <c r="K129">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D130" t="s">
+        <v>45</v>
+      </c>
+      <c r="E130">
+        <v>4.5</v>
+      </c>
+      <c r="F130" t="s">
+        <v>51</v>
+      </c>
+      <c r="G130">
+        <v>4.63</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0.5279999971389771</v>
+      </c>
+      <c r="I130" t="s">
+        <v>53</v>
+      </c>
+      <c r="J130" t="s">
+        <v>57</v>
+      </c>
+      <c r="K130">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" t="s">
+        <v>21</v>
+      </c>
+      <c r="B131" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" t="s">
+        <v>25</v>
+      </c>
+      <c r="D131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E131">
+        <v>20.5</v>
+      </c>
+      <c r="F131" t="s">
+        <v>51</v>
+      </c>
+      <c r="G131">
+        <v>20.85</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0.5279999971389771</v>
+      </c>
+      <c r="I131" t="s">
+        <v>52</v>
+      </c>
+      <c r="J131" t="s">
+        <v>57</v>
+      </c>
+      <c r="K131">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" t="s">
+        <v>11</v>
+      </c>
+      <c r="B132" t="s">
+        <v>25</v>
+      </c>
+      <c r="C132" t="s">
+        <v>26</v>
+      </c>
+      <c r="D132" t="s">
+        <v>36</v>
+      </c>
+      <c r="E132">
+        <v>4.5</v>
+      </c>
+      <c r="F132" t="s">
+        <v>51</v>
+      </c>
+      <c r="G132">
+        <v>4.36</v>
+      </c>
+      <c r="H132" s="1">
+        <v>0.5270000100135803</v>
+      </c>
+      <c r="I132" t="s">
+        <v>52</v>
+      </c>
+      <c r="J132" t="s">
+        <v>57</v>
+      </c>
+      <c r="K132">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" t="s">
+        <v>13</v>
+      </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" t="s">
+        <v>25</v>
+      </c>
+      <c r="D133" t="s">
+        <v>30</v>
+      </c>
+      <c r="E133">
+        <v>22.5</v>
+      </c>
+      <c r="F133" t="s">
+        <v>51</v>
+      </c>
+      <c r="G133">
+        <v>23.63</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0.5260000228881836</v>
+      </c>
+      <c r="I133" t="s">
+        <v>52</v>
+      </c>
+      <c r="J133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" t="s">
+        <v>16</v>
+      </c>
+      <c r="B134" t="s">
+        <v>25</v>
+      </c>
+      <c r="C134" t="s">
+        <v>26</v>
+      </c>
+      <c r="D134" t="s">
+        <v>37</v>
+      </c>
+      <c r="E134">
+        <v>11.5</v>
+      </c>
+      <c r="F134" t="s">
+        <v>51</v>
+      </c>
+      <c r="G134">
+        <v>11.84</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0.5249999761581421</v>
+      </c>
+      <c r="I134" t="s">
+        <v>53</v>
+      </c>
+      <c r="J134" t="s">
+        <v>57</v>
+      </c>
+      <c r="K134">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135" t="s">
+        <v>18</v>
+      </c>
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" t="s">
+        <v>25</v>
+      </c>
+      <c r="D135" t="s">
+        <v>40</v>
+      </c>
+      <c r="E135">
+        <v>1.5</v>
+      </c>
+      <c r="F135" t="s">
+        <v>51</v>
+      </c>
+      <c r="G135">
+        <v>1.29</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0.5220000147819519</v>
+      </c>
+      <c r="I135" t="s">
+        <v>53</v>
+      </c>
+      <c r="J135" t="s">
+        <v>57</v>
+      </c>
+      <c r="K135">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136" t="s">
+        <v>24</v>
+      </c>
+      <c r="B136" t="s">
+        <v>25</v>
+      </c>
+      <c r="C136" t="s">
+        <v>26</v>
+      </c>
+      <c r="D136" t="s">
+        <v>33</v>
+      </c>
+      <c r="E136">
+        <v>4.5</v>
+      </c>
+      <c r="F136" t="s">
+        <v>51</v>
+      </c>
+      <c r="G136">
+        <v>4.69</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0.5220000147819519</v>
+      </c>
+      <c r="I136" t="s">
+        <v>53</v>
+      </c>
+      <c r="J136" t="s">
+        <v>57</v>
+      </c>
+      <c r="K136">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" t="s">
+        <v>23</v>
+      </c>
+      <c r="B137" t="s">
+        <v>25</v>
+      </c>
+      <c r="C137" t="s">
+        <v>26</v>
+      </c>
+      <c r="D137" t="s">
+        <v>47</v>
+      </c>
+      <c r="E137">
+        <v>1.5</v>
+      </c>
+      <c r="F137" t="s">
+        <v>51</v>
+      </c>
+      <c r="G137">
+        <v>1.56</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0.5189999938011169</v>
+      </c>
+      <c r="I137" t="s">
+        <v>53</v>
+      </c>
+      <c r="J137" t="s">
+        <v>57</v>
+      </c>
+      <c r="K137">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" t="s">
+        <v>16</v>
+      </c>
+      <c r="B138" t="s">
+        <v>25</v>
+      </c>
+      <c r="C138" t="s">
+        <v>26</v>
+      </c>
+      <c r="D138" t="s">
+        <v>30</v>
+      </c>
+      <c r="E138">
+        <v>19.5</v>
+      </c>
+      <c r="F138" t="s">
+        <v>51</v>
+      </c>
+      <c r="G138">
+        <v>20.57</v>
+      </c>
+      <c r="H138" s="1">
+        <v>0.5189999938011169</v>
+      </c>
+      <c r="I138" t="s">
+        <v>52</v>
+      </c>
+      <c r="J138" t="s">
+        <v>57</v>
+      </c>
+      <c r="K138">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" t="s">
+        <v>12</v>
+      </c>
+      <c r="B139" t="s">
+        <v>25</v>
+      </c>
+      <c r="C139" t="s">
+        <v>26</v>
+      </c>
+      <c r="D139" t="s">
+        <v>38</v>
+      </c>
+      <c r="E139">
+        <v>1.5</v>
+      </c>
+      <c r="F139" t="s">
+        <v>51</v>
+      </c>
+      <c r="G139">
+        <v>1.34</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0.5180000066757202</v>
+      </c>
+      <c r="I139" t="s">
+        <v>52</v>
+      </c>
+      <c r="J139" t="s">
+        <v>57</v>
+      </c>
+      <c r="K139">
+        <v>-10.7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" t="s">
+        <v>13</v>
+      </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140" t="s">
+        <v>25</v>
+      </c>
+      <c r="D140" t="s">
+        <v>44</v>
+      </c>
+      <c r="E140">
+        <v>4.5</v>
+      </c>
+      <c r="F140" t="s">
+        <v>51</v>
+      </c>
+      <c r="G140">
+        <v>4.46</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0.5170000195503235</v>
+      </c>
+      <c r="I140" t="s">
+        <v>52</v>
+      </c>
+      <c r="J140" t="s">
+        <v>57</v>
+      </c>
+      <c r="K140">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" t="s">
+        <v>23</v>
+      </c>
+      <c r="B141" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141" t="s">
+        <v>26</v>
+      </c>
+      <c r="D141" t="s">
+        <v>36</v>
+      </c>
+      <c r="E141">
+        <v>1.5</v>
+      </c>
+      <c r="F141" t="s">
+        <v>51</v>
+      </c>
+      <c r="G141">
+        <v>1.52</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0.5170000195503235</v>
+      </c>
+      <c r="I141" t="s">
+        <v>53</v>
+      </c>
+      <c r="J141" t="s">
+        <v>57</v>
+      </c>
+      <c r="K141">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="A142" t="s">
+        <v>16</v>
+      </c>
+      <c r="B142" t="s">
+        <v>25</v>
+      </c>
+      <c r="C142" t="s">
+        <v>26</v>
+      </c>
+      <c r="D142" t="s">
+        <v>28</v>
+      </c>
+      <c r="E142">
+        <v>39.05</v>
+      </c>
+      <c r="F142" t="s">
+        <v>51</v>
+      </c>
+      <c r="G142">
+        <v>38.09</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0.515999972820282</v>
+      </c>
+      <c r="I142" t="s">
+        <v>53</v>
+      </c>
+      <c r="J142" t="s">
+        <v>57</v>
+      </c>
+      <c r="K142">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" t="s">
+        <v>21</v>
+      </c>
+      <c r="B143" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" t="s">
+        <v>25</v>
+      </c>
+      <c r="D143" t="s">
         <v>43</v>
       </c>
-      <c r="G122">
-        <v>2.32</v>
-      </c>
-      <c r="H122" s="1">
-        <v>0.5009999871253967</v>
-      </c>
-      <c r="I122" t="s">
+      <c r="E143">
+        <v>1.5</v>
+      </c>
+      <c r="F143" t="s">
+        <v>51</v>
+      </c>
+      <c r="G143">
+        <v>1.82</v>
+      </c>
+      <c r="H143" s="1">
+        <v>0.515999972820282</v>
+      </c>
+      <c r="I143" t="s">
+        <v>53</v>
+      </c>
+      <c r="J143" t="s">
+        <v>57</v>
+      </c>
+      <c r="K143">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144" t="s">
+        <v>22</v>
+      </c>
+      <c r="B144" t="s">
+        <v>26</v>
+      </c>
+      <c r="C144" t="s">
+        <v>25</v>
+      </c>
+      <c r="D144" t="s">
+        <v>38</v>
+      </c>
+      <c r="E144">
+        <v>2.5</v>
+      </c>
+      <c r="F144" t="s">
+        <v>51</v>
+      </c>
+      <c r="G144">
+        <v>2.56</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0.5149999856948853</v>
+      </c>
+      <c r="I144" t="s">
+        <v>53</v>
+      </c>
+      <c r="J144" t="s">
+        <v>57</v>
+      </c>
+      <c r="K144">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="A145" t="s">
+        <v>12</v>
+      </c>
+      <c r="B145" t="s">
+        <v>25</v>
+      </c>
+      <c r="C145" t="s">
+        <v>26</v>
+      </c>
+      <c r="D145" t="s">
         <v>44</v>
       </c>
-      <c r="J122" t="s">
-        <v>49</v>
-      </c>
-      <c r="K122">
-        <v>-7.2</v>
+      <c r="E145">
+        <v>2.5</v>
+      </c>
+      <c r="F145" t="s">
+        <v>51</v>
+      </c>
+      <c r="G145">
+        <v>2.36</v>
+      </c>
+      <c r="H145" s="1">
+        <v>0.5149999856948853</v>
+      </c>
+      <c r="I145" t="s">
+        <v>52</v>
+      </c>
+      <c r="J145" t="s">
+        <v>57</v>
+      </c>
+      <c r="K145">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146" t="s">
+        <v>17</v>
+      </c>
+      <c r="B146" t="s">
+        <v>25</v>
+      </c>
+      <c r="C146" t="s">
+        <v>26</v>
+      </c>
+      <c r="D146" t="s">
+        <v>30</v>
+      </c>
+      <c r="E146">
+        <v>9.5</v>
+      </c>
+      <c r="F146" t="s">
+        <v>51</v>
+      </c>
+      <c r="G146">
+        <v>10.16</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0.5149999856948853</v>
+      </c>
+      <c r="I146" t="s">
+        <v>52</v>
+      </c>
+      <c r="J146" t="s">
+        <v>57</v>
+      </c>
+      <c r="K146">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="A147" t="s">
+        <v>18</v>
+      </c>
+      <c r="B147" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" t="s">
+        <v>25</v>
+      </c>
+      <c r="D147" t="s">
+        <v>37</v>
+      </c>
+      <c r="E147">
+        <v>7.5</v>
+      </c>
+      <c r="F147" t="s">
+        <v>51</v>
+      </c>
+      <c r="G147">
+        <v>7.64</v>
+      </c>
+      <c r="H147" s="1">
+        <v>0.5149999856948853</v>
+      </c>
+      <c r="I147" t="s">
+        <v>53</v>
+      </c>
+      <c r="J147" t="s">
+        <v>57</v>
+      </c>
+      <c r="K147">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" t="s">
+        <v>25</v>
+      </c>
+      <c r="D148" t="s">
+        <v>30</v>
+      </c>
+      <c r="E148">
+        <v>23.5</v>
+      </c>
+      <c r="F148" t="s">
+        <v>51</v>
+      </c>
+      <c r="G148">
+        <v>24.06</v>
+      </c>
+      <c r="H148" s="1">
+        <v>0.5139999985694885</v>
+      </c>
+      <c r="I148" t="s">
+        <v>53</v>
+      </c>
+      <c r="J148" t="s">
+        <v>57</v>
+      </c>
+      <c r="K148">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="A149" t="s">
+        <v>17</v>
+      </c>
+      <c r="B149" t="s">
+        <v>25</v>
+      </c>
+      <c r="C149" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" t="s">
+        <v>37</v>
+      </c>
+      <c r="E149">
+        <v>12.5</v>
+      </c>
+      <c r="F149" t="s">
+        <v>51</v>
+      </c>
+      <c r="G149">
+        <v>12.15</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0.5120000243186951</v>
+      </c>
+      <c r="I149" t="s">
+        <v>52</v>
+      </c>
+      <c r="J149" t="s">
+        <v>57</v>
+      </c>
+      <c r="K149">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="A150" t="s">
+        <v>16</v>
+      </c>
+      <c r="B150" t="s">
+        <v>25</v>
+      </c>
+      <c r="C150" t="s">
+        <v>26</v>
+      </c>
+      <c r="D150" t="s">
+        <v>44</v>
+      </c>
+      <c r="E150">
+        <v>6.5</v>
+      </c>
+      <c r="F150" t="s">
+        <v>51</v>
+      </c>
+      <c r="G150">
+        <v>6.08</v>
+      </c>
+      <c r="H150" s="1">
+        <v>0.5120000243186951</v>
+      </c>
+      <c r="I150" t="s">
+        <v>52</v>
+      </c>
+      <c r="J150" t="s">
+        <v>57</v>
+      </c>
+      <c r="K150">
+        <v>-6.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="A151" t="s">
+        <v>20</v>
+      </c>
+      <c r="B151" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151" t="s">
+        <v>25</v>
+      </c>
+      <c r="D151" t="s">
+        <v>44</v>
+      </c>
+      <c r="E151">
+        <v>3.5</v>
+      </c>
+      <c r="F151" t="s">
+        <v>51</v>
+      </c>
+      <c r="G151">
+        <v>3.25</v>
+      </c>
+      <c r="H151" s="1">
+        <v>0.5109999775886536</v>
+      </c>
+      <c r="I151" t="s">
+        <v>53</v>
+      </c>
+      <c r="J151" t="s">
+        <v>57</v>
+      </c>
+      <c r="K151">
+        <v>-7.1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" t="s">
+        <v>25</v>
+      </c>
+      <c r="D152" t="s">
+        <v>39</v>
+      </c>
+      <c r="E152">
+        <v>1.5</v>
+      </c>
+      <c r="F152" t="s">
+        <v>51</v>
+      </c>
+      <c r="G152">
+        <v>1.25</v>
+      </c>
+      <c r="H152" s="1">
+        <v>0.5080000162124634</v>
+      </c>
+      <c r="I152" t="s">
+        <v>53</v>
+      </c>
+      <c r="J152" t="s">
+        <v>57</v>
+      </c>
+      <c r="K152">
+        <v>-16.7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
+      <c r="A153" t="s">
+        <v>13</v>
+      </c>
+      <c r="B153" t="s">
+        <v>26</v>
+      </c>
+      <c r="C153" t="s">
+        <v>25</v>
+      </c>
+      <c r="D153" t="s">
+        <v>45</v>
+      </c>
+      <c r="E153">
+        <v>4.5</v>
+      </c>
+      <c r="F153" t="s">
+        <v>51</v>
+      </c>
+      <c r="G153">
+        <v>4.6</v>
+      </c>
+      <c r="H153" s="1">
+        <v>0.5059999823570251</v>
+      </c>
+      <c r="I153" t="s">
+        <v>52</v>
+      </c>
+      <c r="J153" t="s">
+        <v>57</v>
+      </c>
+      <c r="K153">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
+      <c r="A154" t="s">
+        <v>16</v>
+      </c>
+      <c r="B154" t="s">
+        <v>25</v>
+      </c>
+      <c r="C154" t="s">
+        <v>26</v>
+      </c>
+      <c r="D154" t="s">
+        <v>47</v>
+      </c>
+      <c r="E154">
+        <v>1.5</v>
+      </c>
+      <c r="F154" t="s">
+        <v>51</v>
+      </c>
+      <c r="G154">
+        <v>1.64</v>
+      </c>
+      <c r="H154" s="1">
+        <v>0.5040000081062317</v>
+      </c>
+      <c r="I154" t="s">
+        <v>53</v>
+      </c>
+      <c r="J154" t="s">
+        <v>57</v>
+      </c>
+      <c r="K154">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
+      <c r="A155" t="s">
+        <v>16</v>
+      </c>
+      <c r="B155" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" t="s">
+        <v>26</v>
+      </c>
+      <c r="D155" t="s">
+        <v>46</v>
+      </c>
+      <c r="E155">
+        <v>6.5</v>
+      </c>
+      <c r="F155" t="s">
+        <v>51</v>
+      </c>
+      <c r="G155">
+        <v>5.83</v>
+      </c>
+      <c r="H155" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I155" t="s">
+        <v>53</v>
+      </c>
+      <c r="J155" t="s">
+        <v>57</v>
+      </c>
+      <c r="K155">
+        <v>-10.3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
+      <c r="A156" t="s">
+        <v>18</v>
+      </c>
+      <c r="B156" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" t="s">
+        <v>25</v>
+      </c>
+      <c r="D156" t="s">
+        <v>27</v>
+      </c>
+      <c r="E156">
+        <v>20.5</v>
+      </c>
+      <c r="F156" t="s">
+        <v>51</v>
+      </c>
+      <c r="G156">
+        <v>20.16</v>
+      </c>
+      <c r="H156" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I156" t="s">
+        <v>52</v>
+      </c>
+      <c r="J156" t="s">
+        <v>57</v>
+      </c>
+      <c r="K156">
+        <v>-1.7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H122">
+  <conditionalFormatting sqref="H2:H156">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>0.585</formula>
     </cfRule>
